--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Лукаш- водитель/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Лукаш- водитель/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.92574063275</v>
+        <v>46157.93116072445</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Лукаш- водитель/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Лукаш- водитель/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93116072445</v>
+        <v>46157.9318258495</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Лукаш- водитель/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Лукаш- водитель/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.9318258495</v>
+        <v>46157.93405340993</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Лукаш- водитель/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Лукаш- водитель/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93405340993</v>
+        <v>46157.93723421765</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Лукаш- водитель/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Лукаш- водитель/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93723421765</v>
+        <v>46158.28221227111</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Лукаш- водитель/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Лукаш- водитель/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.28221227111</v>
+        <v>46158.29701304263</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Лукаш- водитель/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Лукаш- водитель/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29701304263</v>
+        <v>46158.29820923997</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Лукаш- водитель/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Лукаш- водитель/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29820923997</v>
+        <v>46158.33392276624</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Лукаш- водитель/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Лукаш- водитель/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.33392276624</v>
+        <v>46158.36862021194</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Лукаш- водитель/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Лукаш- водитель/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.36862021194</v>
+        <v>46158.37292811657</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
